--- a/courseware/Labs/Lab-03-DMAIC/Starter.xlsx
+++ b/courseware/Labs/Lab-03-DMAIC/Starter.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Create an Excel line chart of delivery_L_h by timestamp for baseline, monitoring and pilot, with the fixed baseline mean/UCL/LCL. Flag points outside the limits without refitting them. Report phase counts and affected IDs. Explain the monitoring shift as a signal requiring investigation, not a proven restriction diagnosis. Keep invalid and missing tests visible in QualityAudit.</t>
+          <t>Review the existing Analysis and SPC_Summary chart. Keep the prepared formulas and fixed baseline limits unchanged. Identify valid monitoring points outside the limits and check one example against the source row. Return only three sentences: observed signal, supporting evidence, and an unresolved limitation. Do not rebuild the chart or calculate capability.</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Add an Excel formula RPN=S*O*D for every row. Sort a view by RPN descending while preserving mode IDs and source rows. Add a separate high-severity review flag for S&gt;=9. Create an RPN column chart. Do not treat rank or low RPN as evidence of safety acceptance.</t>
+          <t>Review the prepared FMEA_Review. Check the RPN formulas for FM01 and FM04, preserving mode IDs and provisional scores. Explain why the severity-9 row still needs review. Return one evidence gap and one proposed action for FM01; keep residual ratings unassessed. Do not rebuild the table or chart.</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Use WeeklyEvents, DefectCounts and Evidence. Draft a DMAIC table in Excel: phase, claim, metric, source, limitation, next action. Define the CTQ as delivery-test acceptance deviation, not chemical compliance. Calculate baseline and pilot rates using summed deviations divided by summed opportunities, not a simple average when denominators differ.</t>
+          <t>Review the prepared Rate_Comparison, WeeklyEvents and DMAIC tables. Check baseline and pilot rates using summed deviations divided by summed opportunities. Return three cells: measured change, limitation and next evidence. Do not create a full report or a new chart, and do not claim a causal effect from the short pilot.</t>
         </is>
       </c>
     </row>

--- a/courseware/Labs/Lab-03-DMAIC/Starter.xlsx
+++ b/courseware/Labs/Lab-03-DMAIC/Starter.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Save a working copy of Starter.xlsx to your approved OneDrive or SharePoint location. Open it in Excel with your work/school account and use the Copilot side pane. Select the named table before prompting. If Copilot cannot edit, request the formula and insert it manually; record the fallback. Confirm tenant entitlement and supported workbook format before class. Keep the local raw files unchanged.</t>
+          <t>For the class, save a working copy of Worked-Reference.xlsx to approved OneDrive or SharePoint storage. Starter.xlsx is optional after-class practice. Open it in Excel with your work/school account and use the Copilot side pane. Select the named table before prompting. If Copilot cannot edit, request the formula and insert it manually; record the fallback. Confirm tenant entitlement and supported workbook format before class. Keep the local raw files unchanged.</t>
         </is>
       </c>
     </row>

--- a/courseware/Labs/Lab-03-DMAIC/Starter.xlsx
+++ b/courseware/Labs/Lab-03-DMAIC/Starter.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +59,17 @@
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00087F8C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00142C3E"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -90,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,6 +118,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,7 +515,6 @@
           <t>Lab 3 - Use Copilot in Excel to create a DMAIC summary</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -777,10 +793,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -822,6 +839,66 @@
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Two formula-based rates and a concise DMAIC table that states the problem, evidence, proposed test, and monitoring rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>RISE prompt builder</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>What this part does</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>R - Role</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Six Sigma project assistant</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>I - Input</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Only WeeklyData; four Baseline and two Pilot weeks</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>S - Steps</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Calculate both rates; create five-row DMAIC summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>E - Expectations</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Show formulas; separate facts from hypotheses; no causal claim</t>
         </is>
       </c>
     </row>
